--- a/social media/C1/Reading3.xlsx
+++ b/social media/C1/Reading3.xlsx
@@ -587,42 +587,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TEND</t>
+          <t>envisage the profound psychological shifts triggered by the relentless pace of rapid urbanization. As populations migrated from rural heartlands to burgeoning metropolises, a noticeable (17) (TEND) toward social alienation emerged among the workforce. To</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>toward social alienation emerged among the workforce. To (18) (SET) the physiological stressors inherent in high-density living, modern urban planners now prioritize the integration of 'green pockets.' However, for many city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HABIT</t>
+          <t>the physiological stressors inherent in high-density living, modern urban planners now prioritize the integration of 'green pockets.' However, for many city (19) (HABIT) , the constant</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>STIMULATE</t>
+          <t>, the constant (20) (STIMULATE) of the senses remains a significant barrier to achieving mental equilibrium. Standing amidst towering glass structures, an individual may frequently experience a crushing sense of their own</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>of the senses remains a significant barrier to achieving mental equilibrium. Standing amidst towering glass structures, an individual may frequently experience a crushing sense of their own (21) (SIGNIFY) This existential unease is often exacerbated by the perceived</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LOSE</t>
+          <t>This existential unease is often exacerbated by the perceived (22) (LOSE) of traditional community ties and ancestral support networks. Despite these psychological hurdles, the</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>of traditional community ties and ancestral support networks. Despite these psychological hurdles, the (23) (RELY) of urban infrastructure and economic opportunity continues to exert a powerful pull. Consequently, the social fabric of the city must be</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>of urban infrastructure and economic opportunity continues to exert a powerful pull. Consequently, the social fabric of the city must be (24) (STRONG) through more empathetic and human-centric architectural design.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WITHDRAW</t>
+          <t>unexpected stroke of luck for the team. However, the (17) (WITHDRAW) of such delicate artifacts requires extreme precision. Any</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALIGN</t>
+          <t>of such delicate artifacts requires extreme precision. Any (18) (ALIGN) of the humidity levels within the chamber could lead to the</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>of the humidity levels within the chamber could lead to the (19) (APPEAR) of the wall paintings. To prevent this,</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CONSERVE</t>
+          <t>of the wall paintings. To prevent this, (20) (CONSERVE) have implemented a state-of-the-art ventilation system. They remain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>have implemented a state-of-the-art ventilation system. They remain (21) (DENY) that the site can be preserved for future generations. Interestingly, the</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>that the site can be preserved for future generations. Interestingly, the (22) (DEEP) of the structure suggests that the original builders possessed an</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SURPASS</t>
+          <t>of the structure suggests that the original builders possessed an (23) (SURPASS) knowledge of structural engineering. This find will undoubtedly</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BROAD</t>
+          <t>knowledge of structural engineering. This find will undoubtedly (24) (BROAD) our understanding of prehistoric social hierarchies.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -837,42 +837,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WITHDRAW</t>
+          <t>remarkable complexity of human decision-making. Recent advances in brain imaging have revealed a clear (17) (DIVIDE) between emotional and rational systems in the brain, suggesting that choices rarely emerge from logic alone. This has led to the</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ALIGN</t>
+          <t>between emotional and rational systems in the brain, suggesting that choices rarely emerge from logic alone. This has led to the (18) (EMERGE) of a new model in which emotion and reason are treated as equally important inputs to any decision. Under conditions of stress, decision-making can become severely</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>of a new model in which emotion and reason are treated as equally important inputs to any decision. Under conditions of stress, decision-making can become severely (19) (IMPAIR), as elevated cortisol levels interfere with the functioning of the prefrontal cortex. Neuroscientists argue that an individual's</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CONSERVE</t>
+          <t>, as elevated cortisol levels interfere with the functioning of the prefrontal cortex. Neuroscientists argue that an individual's (20) (ABLE) to manage such pressures varies considerably from person to person. They have made</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>to manage such pressures varies considerably from person to person. They have made (21) (CONSIDER) progress in identifying the specific neural circuits involved in these processes, though a complete understanding remains some way off. These insights have clear</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DEEP</t>
+          <t>progress in identifying the specific neural circuits involved in these processes, though a complete understanding remains some way off. These insights have clear (22) (IMPLY) for a range of applied fields. Practitioners in medicine, law and economics are now revisiting assumptions that were once treated as</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SURPASS</t>
+          <t>for a range of applied fields. Practitioners in medicine, law and economics are now revisiting assumptions that were once treated as (23) (DISPUTE). It appears almost</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BROAD</t>
+          <t>. It appears almost (24) (AVOID) that future research will continue to transform our understanding of how choices are made.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,42 +962,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>static entity; it is constantly evolving. The (17) (ROOT) of certain dialects can be traced back to historical migrations. When two groups interact, a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MINGLE</t>
+          <t>of certain dialects can be traced back to historical migrations. When two groups interact, a (18) (MINGLE) of linguistic features often occurs, leading to the</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>of linguistic features often occurs, leading to the (19) (CREATE) of new hybrid forms. This process is frequently</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JUDGE</t>
+          <t>of new hybrid forms. This process is frequently (20) (JUDGE) by those who wish to preserve 'pure' language. They view such changes as a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>by those who wish to preserve 'pure' language. They view such changes as a (21) (WEAK) of cultural identity. However, linguists argue that the</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>of cultural identity. However, linguists argue that the (22) (STRONG) of a language lies in its ability to adapt. To</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MYSTERY</t>
+          <t>of a language lies in its ability to adapt. To (23) (MYSTERY) these complex shifts, one must look at the</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RELATION</t>
+          <t>these complex shifts, one must look at the (24) (RELATION) between social status and speech patterns.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,42 +1087,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONSUME</t>
+          <t>unprecedented shift toward ethical consumption. Many (17) (CONSUME) now scrutinize the supply chains of global corporations. This heightened</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AWARE</t>
+          <t>now scrutinize the supply chains of global corporations. This heightened (18) (AWARE) has forced brands to</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JUST</t>
+          <t>has forced brands to (19) (JUST) their production methods. While some critics dismiss this as mere PR, others argue it represents a</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEFINE</t>
+          <t>their production methods. While some critics dismiss this as mere PR, others argue it represents a (20) (DEFINE) of corporate responsibility. The</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SCARCE</t>
+          <t>of corporate responsibility. The (21) (SCARCE) of sustainable goods is no longer a niche market. However, the</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OCCUR</t>
+          <t>of sustainable goods is no longer a niche market. However, the (22) (OCCUR) of 'greenwashing'—where companies make</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LEAD</t>
+          <t>of 'greenwashing'—where companies make (23) (LEAD) environmental claims—remains a concern. To</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MAXIMUM</t>
+          <t>environmental claims—remains a concern. To (24) (MAXIMUM) the impact of their purchases, shoppers are increasingly turning to independent certification labels.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1212,42 +1212,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>perception of time is often subjective. In moments of intense (17) (ENJOY), an hour can feel like a mere minute. This</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FLUID</t>
+          <t>, an hour can feel like a mere minute. This (18) (FLUID) of time is a central theme in many philosophical</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DISCOURSE</t>
+          <t>of time is a central theme in many philosophical (19) (DISCOURSE). Historically, the</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COME</t>
+          <t>. Historically, the (20) (COME) of the clock brought a new</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RIGID</t>
+          <t>of the clock brought a new (21) (RIGID) to daily life. No longer governed by the sun, human</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>to daily life. No longer governed by the sun, human (22) (ACT) became synchronized with mechanical gears. Despite this, the</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>became synchronized with mechanical gears. Despite this, the (23) (SIGNIFY) of our internal biological rhythms cannot be</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LOOK</t>
+          <t>of our internal biological rhythms cannot be (24) (LOOK). Nature still dictates our need for rest.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1337,42 +1337,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LESS</t>
+          <t>expansion of cities has led to significant environmental challenges. Planners are now looking for ways to (17) (LESS) the impact of urban sprawl. One approach is the</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CONVERT</t>
+          <t>the impact of urban sprawl. One approach is the (18) (CONVERT) of derelict industrial sites into green spaces. This</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAXIMUM</t>
+          <t>of derelict industrial sites into green spaces. This (19) (MAXIMUM) of land use not only improves air quality but also fosters a sense of community. Furthermore, the</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MODERN</t>
+          <t>of land use not only improves air quality but also fosters a sense of community. Furthermore, the (20) (MODERN) of public transport systems is essential to reduce car dependency. However, some residents express</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>of public transport systems is essential to reduce car dependency. However, some residents express (21) (TRUST) regarding the cost of these projects. They fear that the</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RICH</t>
+          <t>regarding the cost of these projects. They fear that the (22) (RICH) of certain neighborhoods will lead to higher taxes. Despite these concerns, the</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MAINTAIN</t>
+          <t>of certain neighborhoods will lead to higher taxes. Despite these concerns, the (23) (MAINTAIN) of sustainable policies is</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISPENSE</t>
+          <t>of sustainable policies is (24) (DISPENSE) for the city's long-term health.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1462,42 +1462,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HINDER</t>
+          <t>storage of information. Cognitive scientists have identified various factors that can (17) (HINDER) our ability to recall facts. For instance, high levels of stress can lead to the</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLOCK</t>
+          <t>our ability to recall facts. For instance, high levels of stress can lead to the (18) (BLOCK) of neural pathways. This</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>of neural pathways. This (19) (CONNECT) often results in temporary forgetfulness. To</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>often results in temporary forgetfulness. To (20) (ACT) the effects of aging on the brain, mental exercises are highly recommended. Interestingly, the</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>the effects of aging on the brain, mental exercises are highly recommended. Interestingly, the (21) (LONG) of a memory is often tied to its emotional weight. A</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>of a memory is often tied to its emotional weight. A (22) (SIGNIFY) event is more likely to be encoded deeply. Scientists also warn against the</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CARD</t>
+          <t>event is more likely to be encoded deeply. Scientists also warn against the (23) (ACCUMULATE) of data, as the brain tends to</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONNECT</t>
+          <t>of data, as the brain tends to (24) (CARD) information it deems irrelevant.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1587,42 +1587,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>frontiers of human knowledge. Exploration is difficult due to the (17) (PURE) of the water at great depths. Small</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PERFECT</t>
+          <t>of the water at great depths. Small (18) (PERFECT) in equipment can be fatal under such pressure. Therefore, engineers must</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FORCE</t>
+          <t>in equipment can be fatal under such pressure. Therefore, engineers must (19) (FORCE) every component before a mission. The</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>every component before a mission. The (20) (CLOSE) of new species in these regions has</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>of new species in these regions has (21) (SET) our biological theories. Many of these organisms have adapted to survive in</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PERPETUATE</t>
+          <t>our biological theories. Many of these organisms have adapted to survive in (22) (PERPETUATE) darkness. Protecting these habitats from</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EXPLOIT</t>
+          <t>darkness. Protecting these habitats from (23) (EXPLOIT) is now a global priority. The</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MAP</t>
+          <t>is now a global priority. The (24) (MAP) of the seafloor is a task that will take decades.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,42 +1712,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APPREHEND</t>
+          <t>dread when asked to speak in public. This (17) (APPREHEND) can be so severe that it hinders professional growth. However, mastering the art of</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORATE</t>
+          <t>can be so severe that it hinders professional growth. However, mastering the art of (18) (ORATE) is a skill that can be learned. Experts suggest that</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PREPARE</t>
+          <t>is a skill that can be learned. Experts suggest that (19) (PREPARE) is the key to success. By</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LINE</t>
+          <t>is the key to success. By (20) (LINE) the main points of a speech, a speaker can maintain better focus. Furthermore, the</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DELIVER</t>
+          <t>the main points of a speech, a speaker can maintain better focus. Furthermore, the (21) (DELIVER) of a clear message is more important than using complex vocabulary. To</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CAPAPTIVE</t>
+          <t>of a clear message is more important than using complex vocabulary. To (22) (CAPAPTIVE) the audience, one should use relatable examples. Often, the</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>the audience, one should use relatable examples. Often, the (23) (TRUE) of a speech is what determines its long-term</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>of a speech is what determines its long-term (24) (EFFECT) on the listeners.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1837,42 +1837,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VISION</t>
+          <t>coldness and lack of character. However, new (17) (VISION) are challenging this view by integrating nature into their designs. This</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORPORATE</t>
+          <t>are challenging this view by integrating nature into their designs. This (18) (CORPORATE) of organic elements into concrete structures is known as biophilic design. The</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>of organic elements into concrete structures is known as biophilic design. The (19) (STABLE) of these buildings often depends on the use of sustainable materials. To</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PROOF</t>
+          <t>of these buildings often depends on the use of sustainable materials. To (20) (PROOF) the structure against extreme weather, innovative techniques are employed. The</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BRIGHT</t>
+          <t>the structure against extreme weather, innovative techniques are employed. The (21) (BRIGHT) of the building's facade can also</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HEIGHT</t>
+          <t>of the building's facade can also (22) (HEIGHT) its energy efficiency. Critics often point out the</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>its energy efficiency. Critics often point out the (23) (COST) of such projects, yet their</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BENEFIT</t>
+          <t>of such projects, yet their (24) (BENEFIT) impact on urban well-being is undeniable.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1962,42 +1962,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SLEEP</t>
+          <t>essential for maintaining overall health. Scientists have discovered that (17) (SLEEP) can lead to serious cognitive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IMPEDE</t>
+          <t>can lead to serious cognitive (18) (IMPEDE). During sleep, the brain undergoes a process of</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SOLID</t>
+          <t>. During sleep, the brain undergoes a process of (19) (SOLID) where memories are sorted. To</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MAX</t>
+          <t>where memories are sorted. To (20) (MAX) the quality of rest, one should avoid caffeine late in the day. The</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>the quality of rest, one should avoid caffeine late in the day. The (21) (REGULAR) of sleep cycles is also crucial for waking up refreshed. Many people suffer from</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>INTERRUPT</t>
+          <t>of sleep cycles is also crucial for waking up refreshed. Many people suffer from (22) (INTERRUPT) sleep, which can be caused by stress.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>sleep, which can be caused by stress. (23) (SURPRISE), even a short nap can</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SHARP</t>
+          <t>, even a short nap can (24) (SHARP) your alertness and productivity during the afternoon.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2087,42 +2087,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MOBILE</t>
+          <t>revolutionized the way we think about work. This new found (17) (MOBILE) allows professionals to travel while maintaining their careers. For many, the</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CONFINE</t>
+          <t>allows professionals to travel while maintaining their careers. For many, the (18) (CONFINE) of a traditional office is a thing of the past. However, this lifestyle is not without its</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>of a traditional office is a thing of the past. However, this lifestyle is not without its (19) (SHORT). Loneliness and the</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ABSENT</t>
+          <t>. Loneliness and the (20) (ABSENT) of a stable community can be challenging. To</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COME</t>
+          <t>of a stable community can be challenging. To (21) (COME) these issues, many nomads join co-working spaces. The</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>these issues, many nomads join co-working spaces. The (22) (POPULAR) of these hubs has led to a</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>VITAL</t>
+          <t>of these hubs has led to a (23) (VITAL) of local economies in remote areas.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ADMIT</t>
+          <t>of local economies in remote areas. (24) (ADMIT), the long-term effects on local housing markets are still being debated.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2212,42 +2212,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BREAK</t>
+          <t>global transition to renewable energy is accelerating. Recent (17) (BREAK) in solar panel technology have made it more cost-effective. This has led to an</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PRECEDENT</t>
+          <t>in solar panel technology have made it more cost-effective. This has led to an (18) (PRECEDENT) increase in the number of households adopting green energy. Governments are providing</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>increase in the number of households adopting green energy. Governments are providing (19) (CENT) to encourage the</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PLACE</t>
+          <t>to encourage the (20) (PLACE) of fossil fuels with cleaner alternatives. Scientists are also working on the</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OPTIMUM</t>
+          <t>of fossil fuels with cleaner alternatives. Scientists are also working on the (21) (OPTIMUM) of energy storage systems to ensure a</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>of energy storage systems to ensure a (22) (RELY) supply of electricity. The</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BROAD</t>
+          <t>supply of electricity. The (23) (BROAD) of these technologies is</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CRITIC</t>
+          <t>of these technologies is (24) (CRITIC) for meeting climate targets by 2050.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2337,42 +2337,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PERSON</t>
+          <t>psychological techniques to influence our choices. One common strategy is the (17) (PERSON) of a product through celebrity endorsements. This creates an</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CONSCIOUS</t>
+          <t>of a product through celebrity endorsements. This creates an (18) (CONSCIOUS) association between the brand and success. Another tactic involves creating a sense of</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SCARCE</t>
+          <t>association between the brand and success. Another tactic involves creating a sense of (19) (SCARCE), making shoppers feel they must act</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INSTINCT</t>
+          <t>, making shoppers feel they must act (20) (INSTINCT). Many consumers are</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AWARE</t>
+          <t>. Many consumers are (21) (AWARE) of these subtle manipulations. However,</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IMPROVE</t>
+          <t>of these subtle manipulations. However, (22) (IMPROVE) in financial literacy can help people make more</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>REASON</t>
+          <t>in financial literacy can help people make more (23) (REASON) decisions. Ultimately, understanding our own</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VULNERABLE</t>
+          <t>decisions. Ultimately, understanding our own (24) (VULNERABLE) is the best defense against impulse buying.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2462,42 +2462,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHARACTER</t>
+          <t>originally emerged from the African American communities of New Orleans. It is (17) (CHARACTER) for its swing and blue notes, complex chords, call and response vocals, and improvisation. While some feared the</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>for its swing and blue notes, complex chords, call and response vocals, and improvisation. While some feared the (18) (APPEAR) of traditional structures, jazz actually</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BROAD</t>
+          <t>of traditional structures, jazz actually (19) (BROAD) the horizons of modern music. Talented</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MUSIC</t>
+          <t>the horizons of modern music. Talented (20) (MUSIC) from diverse backgrounds contributed to its growth,</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>from diverse backgrounds contributed to its growth, (21) (SIGNIFY) altering the cultural landscape. Over the decades, many</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>VARY</t>
+          <t>altering the cultural landscape. Over the decades, many (22) (VARY) have appeared, ranging from bebop to fusion. This flexibility</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>have appeared, ranging from bebop to fusion. This flexibility (23) (ABLE) the genre to stay relevant in a fast-paced world. The</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ENDURE</t>
+          <t>the genre to stay relevant in a fast-paced world. The (24) (ENDURE) of jazz is a testament to its profound emotional depth and its ability to reflect the human experience across different eras and continents. It remains a powerful medium of artistic expression that continues to inspire and challenge artists and listeners alike around the globe.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2587,42 +2587,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MYSTERY</t>
+          <t>depths of our oceans reveals a world that remains largely (17) (MYSTERY) to science. For centuries, humans were</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAPABLE</t>
+          <t>to science. For centuries, humans were (18) (CAPABLE) of reaching the seafloor due to the extreme</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PRESS</t>
+          <t>of reaching the seafloor due to the extreme (19) (PRESS) exerted by miles of water. However, recent technological</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DISCOVER</t>
+          <t>exerted by miles of water. However, recent technological (20) (DISCOVER) have allowed us to send remote vehicles into the abyss. Each mission brings a startling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>REVEAL</t>
+          <t>have allowed us to send remote vehicles into the abyss. Each mission brings a startling (21) (REVEAL) about the creatures living there. These organisms have developed unique</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ADAPT</t>
+          <t>about the creatures living there. These organisms have developed unique (22) (ADAPT) to survive in total darkness and freezing temperatures. Their</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SURVIVE</t>
+          <t>to survive in total darkness and freezing temperatures. Their (23) (SURVIVE) depends on nutrients falling from the surface or chemical energy from vents. Scientists have studied these environments</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EXTEND</t>
+          <t>depends on nutrients falling from the surface or chemical energy from vents. Scientists have studied these environments (24) (EXTEND) to understand the origins of life on Earth. Despite these efforts, much of the ocean floor remains unmapped. Protecting these fragile ecosystems is vital for the planet’s health, as they play a crucial role in regulating our climate.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2712,42 +2712,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>critically important ecosystems that store more carbon than all the world's forests combined. They help (17) (STABLE) the global climate by trapping greenhouse gases for thousands of years. Often</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNDERSTAND</t>
+          <t>the global climate by trapping greenhouse gases for thousands of years. Often (18) (UNDERSTAND) as mere wastelands, these wetlands are actually</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BENEFIT</t>
+          <t>as mere wastelands, these wetlands are actually (19) (BENEFIT) to both people and nature. They provide essential</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PROTECT</t>
+          <t>to both people and nature. They provide essential (20) (PROTECT) against flooding by absorbing heavy rainfall like a sponge. From an</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ECOLOGY</t>
+          <t>against flooding by absorbing heavy rainfall like a sponge. From an (21) (ECOLOGY) perspective, they are home to a</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>perspective, they are home to a (22) (RARE) of species that cannot be found elsewhere. Unfortunately, drainage for agriculture</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>THREAT</t>
+          <t>of species that cannot be found elsewhere. Unfortunately, drainage for agriculture (23) (THREAT) these habitats, releasing stored carbon back into the atmosphere. To combat this, conservationists are working</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>these habitats, releasing stored carbon back into the atmosphere. To combat this, conservationists are working (24) (EFFECT) to restore damaged bogs. By rewetting the land, we can ensure these vital areas continue to function as natural carbon sinks. Their preservation is a key strategy in our ongoing fight against rising temperatures and the loss.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2837,42 +2837,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REPEAT</t>
+          <t>undeniably linked to mental strength. Athletes often face (17) (REPEAT) pressure to perform at their best under extreme conditions. Experts argue that</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CONFIDE</t>
+          <t>pressure to perform at their best under extreme conditions. Experts argue that (18) (CONFIDE) is just as important as physical training. Many stars use</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VISUAL</t>
+          <t>is just as important as physical training. Many stars use (19) (VISUAL) techniques to prepare for major competitions. This mental rehearsal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>techniques to prepare for major competitions. This mental rehearsal (20) (STRONG) their focus and reduces anxiety before a race. However, the</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CERTAIN</t>
+          <t>their focus and reduces anxiety before a race. However, the (21) (CERTAIN) of competition means that even the most prepared can fail. Developing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RESILIENT</t>
+          <t>of competition means that even the most prepared can fail. Developing (22) (RESILIENT) is therefore crucial for bouncing back after a loss. Coaches emphasize the</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NECESSARY</t>
+          <t>is therefore crucial for bouncing back after a loss. Coaches emphasize the (23) (NECESSARY) of maintaining a positive mindset regardless of the score. The</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>of maintaining a positive mindset regardless of the score. The (24) (GROW) of sports psychology has transformed how modern teams approach their daily routines. It provides them with the tools needed to overcome internal obstacles and achieve peak performance on the field, ensuring that the mind is as ready as the body for the challenges ahead.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2962,42 +2962,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SUSTAIN</t>
+          <t>arrival of steel and glass changed the way we build our cities. Contemporary architects now focus on (17) (SUSTAIN) and the efficient use of energy. Many</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RESIDENT</t>
+          <t>and the efficient use of energy. Many (18) (RESIDENT) buildings now incorporate vertical gardens to improve air quality. This</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>INNOVATE</t>
+          <t>buildings now incorporate vertical gardens to improve air quality. This (19) (INNOVATE) approach helps to reduce the urban heat island effect. Furthermore, the</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>INSTALL</t>
+          <t>approach helps to reduce the urban heat island effect. Furthermore, the (20) (INSTALL) of solar panels is becoming a standard practice. Despite the</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CRITIC</t>
+          <t>of solar panels is becoming a standard practice. Despite the (21) (CRITIC) from traditionalists who prefer stone structures, modern designs offer more</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FLEXIBLE</t>
+          <t>from traditionalists who prefer stone structures, modern designs offer more (22) (FLEXIBLE) for growing populations. The</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DEVELOP</t>
+          <t>for growing populations. The (23) (DEVELOP) of old industrial areas has breathed new life into many downtown districts. These</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TRANSFORM</t>
+          <t>of old industrial areas has breathed new life into many downtown districts. These (24) (TRANSFORM) prove that cities can evolve while remaining functional and beautiful. By blending technology with environmental awareness, architects are creating spaces that reflect the needs of the future. The result is a skyline that is both visually stunning and responsible, marking a new era for the construction industry and urban living.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3087,42 +3087,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PATIENT</t>
+          <t>enjoyable activity that allows people to express their creativity. To master the art of gastronomy, one needs (17) (PATIENT) and a willingness to experiment with flavors. Many chefs emphasize that the</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FRESH</t>
+          <t>and a willingness to experiment with flavors. Many chefs emphasize that the (18) (FRESH) of ingredients is the key to a successful dish. Adding a</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VARY</t>
+          <t>of ingredients is the key to a successful dish. Adding a (19) (VARY) of herbs can drastically change the profile of a simple meal.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OCCASION</t>
+          <t>of herbs can drastically change the profile of a simple meal. (20) (OCCASION), even professional cooks make mistakes, but these can lead to</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EXPECT</t>
+          <t>, even professional cooks make mistakes, but these can lead to (21) (EXPECT) culinary breakthroughs. The</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>culinary breakthroughs. The (22) (POPULAR) of televised cooking shows has encouraged more people to cook at home. This</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MOVE</t>
+          <t>of televised cooking shows has encouraged more people to cook at home. This (23) (MOVE) has fostered a deeper appreciation for diverse cuisines and traditional techniques. As individuals gain skills, they find that preparing food is not just a daily chore, but a satisfying way to share culture and love with friends and family. Ultimately, the kitchen becomes a place of constant learning and discovery, where every mistake is just a step toward a better meal.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SKILL</t>
+          <t>has fostered a deeper appreciation for diverse cuisines and traditional techniques. As individuals gain (24) (SKILL), they find that preparing food is not just a daily chore, but a satisfying way to share culture and love with friends and family. Ultimately, the kitchen becomes a place of constant learning and discovery, where every mistake is just a step toward a better meal.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3212,42 +3212,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CONCERN</t>
+          <t>revolutionary change thanks to technology. City planners are increasingly (17) (CONCERN) about the impact of traffic congestion on the environment. One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SOLVE</t>
+          <t>about the impact of traffic congestion on the environment. One (18) (SOLVE) is the introduction of electric scooters and bikes. These</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>INNOVATE</t>
+          <t>is the introduction of electric scooters and bikes. These (19) (INNOVATE) aim to reduce our reliance on private cars. Furthermore, the</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EXTEND</t>
+          <t>aim to reduce our reliance on private cars. Furthermore, the (20) (EXTEND) of existing subway lines is seen as</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ESSENCE</t>
+          <t>of existing subway lines is seen as (21) (ESSENCE) for urban growth. Many citizens find that public transport is more</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ECONOMY</t>
+          <t>for urban growth. Many citizens find that public transport is more (22) (ECONOMY) than paying for parking. However, the</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>than paying for parking. However, the (23) (RELY) of these services must be improved to attract more users. With</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>of these services must be improved to attract more users. With (24) (EFFECT) management, cities can become cleaner and more navigable for everyone. By prioritizing green alternatives, we can ensure that future generations enjoy a healthier atmosphere and more efficient ways to travel through their bustling metropolises. This shift requires both political will and public cooperation to succeed in the long term.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3337,42 +3337,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIND</t>
+          <t>widely recognized as a beneficial habit for all ages. It provides (17) (MIND) stimulation that can help slow the progress of cognitive decline. Many people find</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>stimulation that can help slow the progress of cognitive decline. Many people find (18) (ENJOY) in losing themselves in a fictional world. This</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESCAPE</t>
+          <t>in losing themselves in a fictional world. This (19) (ESCAPE) allows individuals to manage their stress levels</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>allows individuals to manage their stress levels (20) (SUCCESS). Moreover, reading</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RICH</t>
+          <t>. Moreover, reading (21) (RICH) our vocabulary and improves our writing skills. There is a great</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>our vocabulary and improves our writing skills. There is a great (22) (LIKE) that avid readers will have better communication abilities.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>that avid readers will have better communication abilities. (23) (REGARD) of the genre, whether it is history or fantasy, the</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KNOW</t>
+          <t>of the genre, whether it is history or fantasy, the (24) (KNOW) gained is invaluable for personal development. It opens up new perspectives and fosters empathy by allowing us to experience lives very different from our own. In an increasingly digital world, the simple act of turning a page remains one of the most effective ways to sharpen the mind and broaden one's understanding of the world.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3462,42 +3462,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRESERVE</t>
+          <t>invention, photography has changed the way we document history. It allows for the (17) (PRESERVE) of moments that would otherwise be forgotten. For many, taking photos is an</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EXPRESS</t>
+          <t>of moments that would otherwise be forgotten. For many, taking photos is an (18) (EXPRESS) of their unique artistic vision. Modern cameras are</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SURPRISE</t>
+          <t>of their unique artistic vision. Modern cameras are (19) (SURPRISE) easy to use, making photography accessible to everyone. However, being a</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PROFESSION</t>
+          <t>easy to use, making photography accessible to everyone. However, being a (20) (PROFESSION) requires a deep understanding of light and composition.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PHOTOGRAPH</t>
+          <t>requires a deep understanding of light and composition. (21) (PHOTOGRAPH) must often wait for hours to capture the perfect shot. This</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PATIENT</t>
+          <t>must often wait for hours to capture the perfect shot. This (22) (PATIENT) is what separates a snapshot from a masterpiece. The</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>is what separates a snapshot from a masterpiece. The (23) (POPULAR) of social media has further increased the</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>VISIBLE</t>
+          <t>of social media has further increased the (24) (VISIBLE) of visual arts in our daily lives. Today, images circulate faster than ever, shaping our perceptions of world events and personal stories alike. A single photograph can spark a global conversation or inspire a change in policy, proving that the lens is a truly powerful tool in the modern digital age.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3587,42 +3587,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DEFICIENT</t>
+          <t>essential for maintaining our physical and mental health. Scientists have discovered that a (17) (DEFICIENT) in sleep can lead to serious long-term health issues. While we rest, the brain performing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COUNT</t>
+          <t>in sleep can lead to serious long-term health issues. While we rest, the brain performing (18) (COUNT) functions that help us process information from the day. This</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AUTOMATON</t>
+          <t>functions that help us process information from the day. This (19) (AUTOMATON) process is vital for memory consolidation and emotional regulation. Many people find it</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>INCREASE</t>
+          <t>process is vital for memory consolidation and emotional regulation. Many people find it (20) (INCREASE) difficult to switch off their devices before bed. However, the</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADOPT</t>
+          <t>difficult to switch off their devices before bed. However, the (21) (ADOPT) of a strict routine can significantly improve sleep quality.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LACK</t>
+          <t>of a strict routine can significantly improve sleep quality. (22) (LACK) a proper rest, our productivity and</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CONCENTRATE</t>
+          <t>a proper rest, our productivity and (23) (CONCENTRATE) levels tend to plummet during working hours. Therefore, making sleep a priority is not a luxury but a</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>REQUIRE</t>
+          <t>levels tend to plummet during working hours. Therefore, making sleep a priority is not a luxury but a (24) (REQUIRE) for a balanced life. By understanding the biological needs of our bodies, we can better appreciate the restorative power of a good night's sleep and its impact on our overall well-being and daily performance.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3712,42 +3712,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PARTICULAR</t>
+          <t>growth of online shopping has revolutionized the retail industry worldwide. This shift has been (17) (PARTICULAR) evident in the last decade, as technology becomes more accessible. For many consumers, the</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CONVENIENT</t>
+          <t>evident in the last decade, as technology becomes more accessible. For many consumers, the (18) (CONVENIENT) of buying from home outweighs the traditional shopping experience. However, this trend has led to the</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>of buying from home outweighs the traditional shopping experience. However, this trend has led to the (19) (CLOSE) of many physical stores on the high street. Business owners must now be</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>COMPETE</t>
+          <t>of many physical stores on the high street. Business owners must now be (20) (COMPETE) in a global market to survive. Providing</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EXCEPT</t>
+          <t>in a global market to survive. Providing (21) (EXCEPT) customer service is more important than ever to build brand loyalty. Furthermore, the</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>customer service is more important than ever to build brand loyalty. Furthermore, the (22) (SECURITY) of online transactions remains a top priority for</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ANXIETY</t>
+          <t>of online transactions remains a top priority for (23) (ANXIETY) shoppers.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FORTUNE</t>
+          <t>shoppers. (24) (FORTUNE), improvements in encryption have made digital payments much safer. As a result, the digital marketplace continues to expand, offering a vast array of products that were previously difficult to find, thus changing the way we perceive and engage with commerce in our daily lives.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3837,42 +3837,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HEAVY</t>
+          <t>commitment to reducing carbon emissions has led to a surge in green technology. Many countries are now (17) (HEAVY) investing in wind and solar power. This</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TRANSIT</t>
+          <t>investing in wind and solar power. This (18) (TRANSIT) away from fossil fuels is necessary for environmental protection. Scientists are working on</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SOLVE</t>
+          <t>away from fossil fuels is necessary for environmental protection. Scientists are working on (19) (SOLVE) to store energy more efficiently for later use. The</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AVAILABLE</t>
+          <t>to store energy more efficiently for later use. The (20) (AVAILABLE) of affordable renewable energy is crucial for developing nations. Despite some</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGREE</t>
+          <t>of affordable renewable energy is crucial for developing nations. Despite some (21) (AGREE) regarding the cost, the long-term benefits are</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>regarding the cost, the long-term benefits are (22) (CLEAR) superior.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ENVIRONMENT</t>
+          <t>superior. (23) (ENVIRONMENT) argue that we must act now to prevent irreversible damage. The</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>argue that we must act now to prevent irreversible damage. The (24) (SUCCESS) implementation of these policies will determine the future of our planet. By embracing innovation and sustainable practices, we can build a resilient energy infrastructure that supports both economic growth and ecological health, ensuring a cleaner and more stable world for the coming generations and beyond.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3962,42 +3962,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEAN</t>
+          <t>controversy among critics and the public alike. While some view abstract pieces as (17) (MEAN), others see them as a profound expression of the human condition. The</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>, others see them as a profound expression of the human condition. The (18) (REJECT) of traditional techniques in the early 20th century allowed artists to explore new</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POSSIBLE</t>
+          <t>of traditional techniques in the early 20th century allowed artists to explore new (19) (POSSIBLE). This movement was</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CHARACTER</t>
+          <t>. This movement was (20) (CHARACTER) by a desire to challenge the status quo and provoke thought. Many galleries now focus on the</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EXHIBIT</t>
+          <t>by a desire to challenge the status quo and provoke thought. Many galleries now focus on the (21) (EXHIBIT) of digital works that incorporate interactive elements. These</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INNOVATE</t>
+          <t>of digital works that incorporate interactive elements. These (22) (INNOVATE) have made art more accessible to a</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BROAD</t>
+          <t>have made art more accessible to a (23) (BROAD) diverse audience. The</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>diverse audience. The (24) (SIGNIFY) of modern art lies in its ability to reflect the complexities of contemporary life. By breaking away from the constraints of realism, artists can communicate emotions and ideas that are often difficult to put into words, fostering a deeper</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4087,42 +4087,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>REMARK</t>
+          <t>relationship between diet and health is crucial for a long life. Nutritional science has made (17) (REMARK) progress in identifying the vitamins we need. A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BALANCE</t>
+          <t>progress in identifying the vitamins we need. A (18) (BALANCE) diet provides the body with enough energy to function</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>diet provides the body with enough energy to function (19) (EFFECT). However, the</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CONSUME</t>
+          <t>. However, the (20) (CONSUME) of processed foods high in sugar has led to an</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ALARM</t>
+          <t>of processed foods high in sugar has led to an (21) (ALARM) increase in obesity rates. Health</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PROFESSION</t>
+          <t>increase in obesity rates. Health (22) (PROFESSION) recommend eating more whole grains and fresh vegetables. This</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ADVISE</t>
+          <t>recommend eating more whole grains and fresh vegetables. This (23) (ADVISE) is often ignored due to the</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CONVENIENT</t>
+          <t>is often ignored due to the (24) (CONVENIENT) of fast food options in modern cities. To improve public health,</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4212,42 +4212,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DEVELOP</t>
+          <t>possibility of living on other planets has fascinated humans for decades. With the (17) (DEVELOP) of powerful rockets, Mars has become a primary target. Scientists are studying the</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HABIT</t>
+          <t>of powerful rockets, Mars has become a primary target. Scientists are studying the (18) (HABIT) of the red planet to see if it can support life. One major</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LIMIT</t>
+          <t>of the red planet to see if it can support life. One major (19) (LIMIT) is the lack of a breathable atmosphere. To overcome this,</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RESEARCH</t>
+          <t>is the lack of a breathable atmosphere. To overcome this, (20) (RESEARCH) are looking into terraforming techniques. This</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AMBITION</t>
+          <t>are looking into terraforming techniques. This (21) (AMBITION) goal requires</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NATION</t>
+          <t>goal requires (22) (NATION) cooperation and vast amounts of funding. Many believe that the</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DISCOVER</t>
+          <t>cooperation and vast amounts of funding. Many believe that the (23) (DISCOVER) of liquid water is a</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>of liquid water is a (24) (SIGNIFY) step forward. However, the</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4337,42 +4337,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>essential for personal growth. Psychologists distinguish between intrinsic and extrinsic motivation, both of which are (17) (SIGNIFY) in different contexts. While rewards can be</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>in different contexts. While rewards can be (18) (EFFECT) in the short term, long-term</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>COMMIT</t>
+          <t>in the short term, long-term (19) (COMMIT) usually comes from within. Many individuals find that setting</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>usually comes from within. Many individuals find that setting (20) (REAL) targets helps maintain their focus and prevents</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FRUSTRATE</t>
+          <t>targets helps maintain their focus and prevents (21) (FRUSTRATE). Furthermore, the</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>RECOGNIZE</t>
+          <t>. Furthermore, the (22) (RECOGNIZE) of small achievements can boost self-esteem and</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>of small achievements can boost self-esteem and (23) (STRONG) one's resolve. However, maintaining a high level of</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ENTHUSIAST</t>
+          <t>one's resolve. However, maintaining a high level of (24) (ENTHUSIAST) can be challenging when faced with setbacks. To overcome these, one must develop a resilient mindset and learn to view failures as</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4462,42 +4462,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REVOLUTION</t>
+          <t>invention of the printing press by Johannes Gutenberg in the 15th century was a (17) (REVOLUTION) moment. Before this, books were</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PAIN</t>
+          <t>moment. Before this, books were (18) (PAIN) slow to produce, as they had to be copied by hand. This</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LIMIT</t>
+          <t>slow to produce, as they had to be copied by hand. This (19) (LIMIT) meant that knowledge was restricted to a wealthy elite. However, the new technology made books more</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AFFORD</t>
+          <t>meant that knowledge was restricted to a wealthy elite. However, the new technology made books more (20) (AFFORD) for the general public. As a result,</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LITERATE</t>
+          <t>for the general public. As a result, (21) (LITERATE) rates began to rise</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DRAMA</t>
+          <t>rates began to rise (22) (DRAMA) across Europe. The</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AVAILABLE</t>
+          <t>across Europe. The (23) (AVAILABLE) of information encouraged people to think for themselves and challenge</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRADITION</t>
+          <t>of information encouraged people to think for themselves and challenge (24) (TRADITION) beliefs. This period of</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4587,42 +4587,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>preservation of biodiversity is vital for the health of our planet. Healthy ecosystems provide (17) (NUMBER) benefits, from clean air to fertile soil. However, human activities such as</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FOREST</t>
+          <t>benefits, from clean air to fertile soil. However, human activities such as (18) (FOREST) are causing a rapid</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LOSE</t>
+          <t>are causing a rapid (19) (LOSE) of species. This</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DESTROY</t>
+          <t>of species. This (20) (DESTROY) of natural habitats disrupts the delicate balance of nature.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ENVIRONMENT</t>
+          <t>of natural habitats disrupts the delicate balance of nature. (21) (ENVIRONMENT) are working tirelessly to protect</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DANGER</t>
+          <t>are working tirelessly to protect (22) (DANGER) animals from extinction. They argue that the</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RESTORE</t>
+          <t>animals from extinction. They argue that the (23) (RESTORE) of damaged landscapes is</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CRITIC</t>
+          <t>of damaged landscapes is (24) (CRITIC) important for our survival. By promoting</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4712,42 +4712,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>overwhelming information, the ability to think critically is more (17) (VALUE) than ever. This skill allows individuals to</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ANALYSIS</t>
+          <t>than ever. This skill allows individuals to (18) (ANALYSIS) arguments and identify potential biases in media reports. Without a</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LOGIC</t>
+          <t>arguments and identify potential biases in media reports. Without a (19) (LOGIC) approach, it is easy to be misled by</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ACCURATE</t>
+          <t>approach, it is easy to be misled by (20) (ACCURATE) data or emotional appeals. Education systems are now</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>data or emotional appeals. Education systems are now (21) (STRONG) their focus on these cognitive abilities to prepare students for the</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CERTAIN</t>
+          <t>their focus on these cognitive abilities to prepare students for the (22) (CERTAIN) of the future.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DEPEND</t>
+          <t>of the future. (23) (DEPEND) thinkers are better equipped to solve complex problems and make informed</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JUDGE</t>
+          <t>thinkers are better equipped to solve complex problems and make informed (24) (JUDGE) in their personal and professional lives. By questioning assumptions and seeking evidence, we can develop a deeper understanding of the world around us. This process not only enhances our decision-making but also fosters a more</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4837,42 +4837,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>dynamic system that is constantly evolving to reflect social changes. The (17) (APPEAR) of new technologies often leads to the</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>of new technologies often leads to the (18) (CREATE) of original words and phrases. While some</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LANGUAGE</t>
+          <t>of original words and phrases. While some (19) (LANGUAGE) worry that digital communication is</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>worry that digital communication is (20) (WEAK) our grammar, others argue it is simply a new form of</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EXPRESS</t>
+          <t>our grammar, others argue it is simply a new form of (21) (EXPRESS). The</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>. The (22) (GLOBAL) of the internet has also encouraged the</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ADOPT</t>
+          <t>of the internet has also encouraged the (23) (ADOPT) of loanwords from different cultures. This</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>RICH</t>
+          <t>of loanwords from different cultures. This (24) (RICH) makes language more versatile and inclusive.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4962,42 +4962,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ORGANISE</t>
+          <t>significant increase in the awareness of mental health issues. Many (17) (ORGANISE) are now providing more</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>are now providing more (18) (SUPPORT) environments for their employees. This</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RECOGNIZE</t>
+          <t>environments for their employees. This (19) (RECOGNIZE) that well-being is as important as physical health is</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EXTREME</t>
+          <t>that well-being is as important as physical health is (20) (EXTREME) beneficial.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FORTUNE</t>
+          <t>beneficial. (21) (FORTUNE), some people still face</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DISCRIMINATE</t>
+          <t>, some people still face (22) (DISCRIMINATE) due to the stigma attached to these conditions. To combat this,</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>EDUCATION</t>
+          <t>due to the stigma attached to these conditions. To combat this, (23) (EDUCATION) campaigns aim to promote</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ACCEPT</t>
+          <t>campaigns aim to promote (24) (ACCEPT) and understanding. By fostering open</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5087,42 +5087,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHARITY</t>
+          <t>rewarding experience that benefits both the individual and the community. Engaging in (17) (CHARITY) work allows people to develop new skills while supporting a good cause. Many find that the</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SATISFY</t>
+          <t>work allows people to develop new skills while supporting a good cause. Many find that the (18) (SATISFY) gained from helping others is</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>COMPARE</t>
+          <t>gained from helping others is (19) (COMPARE) to any monetary gain. Furthermore, volunteering can</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>to any monetary gain. Furthermore, volunteering can (20) (STRONG) social bonds and reduce feelings of</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ALONE</t>
+          <t>social bonds and reduce feelings of (21) (ALONE) among participants. It provides an</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OPPORTUNE</t>
+          <t>among participants. It provides an (22) (OPPORTUNE) to meet people from diverse backgrounds, fostering a sense of</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BELONG</t>
+          <t>to meet people from diverse backgrounds, fostering a sense of (23) (BELONG).</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ADMIT</t>
+          <t>. (24) (ADMIT), it requires a significant time commitment, but the personal growth achieved is invaluable. By contributing to the well-being of others, volunteers gain a broader perspective on life and a deeper understanding of the challenges faced by their neighbors, ultimately creating a more compassionate and cohesive society where everyone has the chance to thrive and feel valued for their unique contributions.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5212,42 +5212,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUTOMATON</t>
+          <t>rapidly transforming the way we live and work. From (17) (AUTOMATON) assistants to complex data analysis, its</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>APPLY</t>
+          <t>assistants to complex data analysis, its (18) (APPLY) are vast. While some fear the</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PLACE</t>
+          <t>are vast. While some fear the (19) (PLACE) of workers, others argue that AI will create new</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMPLOY</t>
+          <t>of workers, others argue that AI will create new (20) (EMPLOY) opportunities in tech-driven sectors. The</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ACCURATE</t>
+          <t>opportunities in tech-driven sectors. The (21) (ACCURATE) of AI systems in medical diagnosis is already</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IMPRESS</t>
+          <t>of AI systems in medical diagnosis is already (22) (IMPRESS). However,</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ETHICS</t>
+          <t>. However, (23) (ETHICS) concerns regarding privacy and bias must be addressed</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EFFECT</t>
+          <t>concerns regarding privacy and bias must be addressed (24) (EFFECT). As we integrate AI into our daily routines, it is crucial to ensure that its development is aligned with human values. By fostering a collaborative approach between humans and machines, we can harness the power of technology to solve some of the world's most pressing challenges, ensuring a future where innovation serves the common good and enhances the quality of life for people everywhere, regardless of their background or location.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5337,42 +5337,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>STORY</t>
+          <t>inception, cinema has been a powerful medium for (17) (STORY). It combines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VISION</t>
+          <t>. It combines (18) (VISION) arts with music and performance to create an</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FORGET</t>
+          <t>arts with music and performance to create an (19) (FORGET) experience. Filmmakers use</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IMAGINE</t>
+          <t>experience. Filmmakers use (20) (IMAGINE) techniques to transport audiences to different worlds. The</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>techniques to transport audiences to different worlds. The (21) (POPULAR) of blockbuster movies</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SURE</t>
+          <t>of blockbuster movies (22) (SURE) that the industry remains</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>that the industry remains (23) (FINANCE) viable. However, independent films often provide more</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>THOUGHT</t>
+          <t>viable. However, independent films often provide more (24) (THOUGHT) explorations of social issues. By reflecting the diversity of human experience, cinema fosters empathy and understanding across cultures. Whether through laughter or tears, movies have the unique ability to connect people, sparking conversations that transcend borders. As technology continues to evolve, from silent black-and-white films to immersive virtual reality, the core essence of cinema remains the same: the desire to share stories that resonate with the heart and mind, inspiring us to see the world through a different lens and appreciate the beauty of our shared humanity.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5462,42 +5462,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>legendary for its grueling distance and the physical toll it takes on runners. It commemorates the (17) (RUN) Pheidippides, who supposedly delivered a message of victory to Athens. Modern marathons have gained</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WORLD</t>
+          <t>Pheidippides, who supposedly delivered a message of victory to Athens. Modern marathons have gained (18) (WORLD) fame, attracting thousands of</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>COMPETE</t>
+          <t>fame, attracting thousands of (19) (COMPETE) each year. Participation requires</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ORDINARY</t>
+          <t>each year. Participation requires (20) (ORDINARY) levels of stamina and mental</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>levels of stamina and mental (21) (TOUGH). While many run for personal</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SATISFY</t>
+          <t>. While many run for personal (22) (SATISFY), others aim to raise money for various</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CHARITY</t>
+          <t>, others aim to raise money for various (23) (CHARITY). The</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>. The (24) (POPULAR) of the event has led to races being held in iconic cities across the globe. For many athletes, completing those 42 kilometers is a life-changing achievement that symbolizes the triumph of the human spirit over physical limitations and exhaustion, proving that with enough dedication and training, almost any obstacle can be overcome and any goal can be reached by those who persevere against all odds.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5587,42 +5587,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RELIEVE</t>
+          <t>universally recognized as a sign of joy and social connection. Scientists have found that it triggers the (17) (RELIEVE) of endorphins, our body's natural feel-good chemicals. This</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BENEFIT</t>
+          <t>of endorphins, our body's natural feel-good chemicals. This (18) (BENEFIT) response helps to reduce stress and improve our</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IMMUNE</t>
+          <t>response helps to reduce stress and improve our (19) (IMMUNE) system. Interestingly, laughter is often</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CONTAGION</t>
+          <t>system. Interestingly, laughter is often (20) (CONTAGION); when we hear someone else laugh, we feel an</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RESIST</t>
+          <t>; when we hear someone else laugh, we feel an (21) (RESIST) urge to join in. From an</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>urge to join in. From an (22) (EVOLVE) perspective, this shared behavior</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>perspective, this shared behavior (23) (STRONG) group bonds and promotes cooperation. Despite its</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SIMPLE</t>
+          <t>group bonds and promotes cooperation. Despite its (24) (SIMPLE), the act of laughing is a complex neurological process that involves multiple areas of the brain. It serves as a vital tool for human interaction, helping us navigate social situations and build lasting relationships based on mutual happiness and understanding, ultimately making our lives richer and more enjoyable through the simple power of a shared smile and a genuine laugh.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5712,42 +5712,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VACANCY</t>
+          <t>remarkable rise in popularity over the last few years. Transforming (17) (VACANCY) lots into green spaces provides</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>lots into green spaces provides (18) (NUMBER) benefits for city dwellers. These gardens encourage the</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PRODUCE</t>
+          <t>benefits for city dwellers. These gardens encourage the (19) (PRODUCE) of fresh, local food and reduce the</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>of fresh, local food and reduce the (20) (RELY) on long-distance transport. Furthermore, they offer</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EDUCATION</t>
+          <t>on long-distance transport. Furthermore, they offer (21) (EDUCATION) opportunities for children to learn about nature. The</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INVOLVE</t>
+          <t>opportunities for children to learn about nature. The (22) (INVOLVE) of the local community is</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ESSENCE</t>
+          <t>of the local community is (23) (ESSENCE) for the success of these projects.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FORTUNE</t>
+          <t>for the success of these projects. (24) (FORTUNE), finding suitable space in crowded cities can be difficult. However, with creative</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5837,42 +5837,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INCREASE</t>
+          <t>traditional office environment has undergone a massive transformation in recent years. Advances in technology have made it (17) (INCREASE) easy for employees to work from home. This shift offers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FLEXIBLE</t>
+          <t>easy for employees to work from home. This shift offers (18) (FLEXIBLE) that was previously unavailable to many workers. Companies have noted that</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PRODUCE</t>
+          <t>that was previously unavailable to many workers. Companies have noted that (19) (PRODUCE) often remains high, or even improves, outside the office. However, the</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ABSENT</t>
+          <t>often remains high, or even improves, outside the office. However, the (20) (ABSENT) of face-to-face interaction can lead to feelings of</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ISOLATE</t>
+          <t>of face-to-face interaction can lead to feelings of (21) (ISOLATE). To combat this, managers are</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>. To combat this, managers are (22) (STRONG) their use of virtual meetings to maintain team spirit. The</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
+          <t>their use of virtual meetings to maintain team spirit. The (23) (SUCCESS) implementation of remote work requires clear communication and trust.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CONSEQUENT</t>
+          <t>implementation of remote work requires clear communication and trust. (24) (CONSEQUENT), many businesses are adopting hybrid models that combine the benefits of both home and office settings, ensuring that employees stay connected while enjoying a better work-life balance and the freedom to manage their own schedules more effectively in a rapidly changing professional landscape.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5962,42 +5962,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>crucial role in our ecosystem as the primary pollinators of many crops. Their (17) (APPEAR) would have a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DISASTER</t>
+          <t>would have a (18) (DISASTER) impact on global food security.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SCIENCE</t>
+          <t>impact on global food security. (19) (SCIENCE) are concerned about the declining populations due to habitat loss and pesticides. This</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>REDUCE</t>
+          <t>are concerned about the declining populations due to habitat loss and pesticides. This (20) (REDUCE) in bee numbers threatens the</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SURVIVE</t>
+          <t>in bee numbers threatens the (21) (SURVIVE) of various plant species.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FORTUNE</t>
+          <t>of various plant species. (22) (FORTUNE), many people are now creating bee-friendly gardens to provide a</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>, many people are now creating bee-friendly gardens to provide a (23) (SAFE) haven for these insects. Public</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AWARE</t>
+          <t>haven for these insects. Public (24) (AWARE) campaigns are also helping to educate people about the importance of protecting bees. By choosing organic products and planting native flowers, we can contribute to the preservation of these vital creatures. Ensuring their future is not just about saving an insect, but about maintaining the delicate balance of nature that supports all life on Earth, providing us with the resources we need to thrive and sustain our planet for generations to come.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6087,42 +6087,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHEER</t>
+          <t>extraordinary power to influence our emotions and mood. Whether it is a (17) (CHEER) melody or a sad song, music can transport us to another place. For many</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MUSIC</t>
+          <t>melody or a sad song, music can transport us to another place. For many (18) (MUSIC), performing is a way to express their</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INNER</t>
+          <t>, performing is a way to express their (19) (INNER) thoughts and feelings. The</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>thoughts and feelings. The (20) (POPULAR) of live concerts proves that people still value the</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONNECT</t>
+          <t>of live concerts proves that people still value the (21) (CONNECT) of shared musical experiences. Furthermore, learning an instrument can be</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>of shared musical experiences. Furthermore, learning an instrument can be (22) (HIGH) beneficial for cognitive development in children.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>REGARD</t>
+          <t>beneficial for cognitive development in children. (23) (REGARD) of the genre, music fosters</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>of the genre, music fosters (24) (CREATE) and provides a sense of comfort during difficult times. By listening to diverse sounds and rhythms, we can broaden our cultural horizons and appreciate the universal language that unites people across the globe. Music is more than just sound; it is a fundamental part of the human experience that enriches our souls and helps us celebrate the beauty and complexity of life in all its many forms and expressions.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6212,42 +6212,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADVANCE</t>
+          <t>mysterious places on Earth. Despite technological (17) (ADVANCE), much of the sea floor remains unmapped. The</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DARK</t>
+          <t>, much of the sea floor remains unmapped. The (18) (DARK) and extreme pressure make it incredibly difficult for humans to explore these regions directly.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CONSEQUENT</t>
+          <t>and extreme pressure make it incredibly difficult for humans to explore these regions directly. (19) (CONSEQUENT), scientists rely on</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>REMOTE</t>
+          <t>, scientists rely on (20) (REMOTE) operated vehicles to collect samples. These machines have led to the</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DISCOVER</t>
+          <t>operated vehicles to collect samples. These machines have led to the (21) (DISCOVER) of bizarre creatures that thrive in</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SEEM</t>
+          <t>of bizarre creatures that thrive in (22) (SEEM) hostile environments. The</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EXIST</t>
+          <t>hostile environments. The (23) (EXIST) of life near hydrothermal vents has challenged our understanding of biology. Many researchers believe that the</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PROTECT</t>
+          <t>of life near hydrothermal vents has challenged our understanding of biology. Many researchers believe that the (24) (PROTECT) of these fragile ecosystems is vital for the planet's health. By studying these unique organisms, we gain insights into the origins of life and the resilience of nature in the face of extreme conditions, ensuring that our knowledge of the world continues to grow as we push the boundaries of what is possible in the deep blue.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6337,42 +6337,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SOCIETY</t>
+          <t>powerful form of self-expression that changes with the seasons. Throughout history, clothing has been used to indicate (17) (SOCIETY) status and cultural identity. The</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>APPEAR</t>
+          <t>status and cultural identity. The (18) (APPEAR) of mass-produced garments in the 20th century made trendy styles more</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ACCESS</t>
+          <t>of mass-produced garments in the 20th century made trendy styles more (19) (ACCESS) to the general public. However, the</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>POPULAR</t>
+          <t>to the general public. However, the (20) (POPULAR) of 'fast fashion' has raised concerns about</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SUSTAIN</t>
+          <t>of 'fast fashion' has raised concerns about (21) (SUSTAIN). Many</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DESIGN</t>
+          <t>. Many (22) (DESIGN) are now focusing on eco-friendly materials to reduce waste. This</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MOVE</t>
+          <t>are now focusing on eco-friendly materials to reduce waste. This (23) (MOVE) towards ethical fashion encourages consumers to value quality over quantity.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ORIGIN</t>
+          <t>towards ethical fashion encourages consumers to value quality over quantity. (24) (ORIGIN), clothes were made to last for years, and a return to this mindset is seen as essential for the planet. By choosing timeless pieces and supporting brands that prioritize fair labor practices, individuals can create a wardrobe that is both stylish and responsible, proving that looking good does not have to come at a cost to the environment or the people who make our clothes.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6462,42 +6462,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>enough rest is vital for our overall well-being. Sleep plays a (17) (SIGNIFY) role in brain function and physical health. A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PERSIST</t>
+          <t>role in brain function and physical health. A (18) (PERSIST) lack of sleep can lead to serious</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MEDICINE</t>
+          <t>lack of sleep can lead to serious (19) (MEDICINE) conditions, such as heart disease. During the night, the body performs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ESSENCE</t>
+          <t>conditions, such as heart disease. During the night, the body performs (20) (ESSENCE) repair work on cells and tissues. Furthermore, sleep is</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CRITIC</t>
+          <t>repair work on cells and tissues. Furthermore, sleep is (21) (CRITIC) for memory consolidation and emotional</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>for memory consolidation and emotional (22) (STABLE).</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FORTUNE</t>
+          <t>. (23) (FORTUNE), many people prioritize work or entertainment over rest, leading to chronic</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TIRE</t>
+          <t>, many people prioritize work or entertainment over rest, leading to chronic (24) (TIRE). To improve sleep quality, experts recommend a consistent bedtime routine. By creating a calm environment and avoiding screens before bed, we can ensure that our minds and bodies get the recovery they need to face the challenges of the next day, ultimately enhancing our productivity and happiness in all aspects of our lives, from professional tasks to personal interactions and physical activities.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6587,42 +6587,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COMMUNICATE</t>
+          <t>globalized world, being bilingual offers numerous advantages. Beyond the obvious benefit of (17) (COMMUNICATE), it also enhances cognitive abilities. Research suggests that</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LANGUAGE</t>
+          <t>, it also enhances cognitive abilities. Research suggests that (18) (LANGUAGE) individuals often possess better problem-solving skills and a more</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>individuals often possess better problem-solving skills and a more (19) (FLEX) mindset. This mental</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>mindset. This mental (20) (AGILE) is particularly useful in professional environments where quick thinking is required. Furthermore, learning a new language fosters</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CULTURE</t>
+          <t>is particularly useful in professional environments where quick thinking is required. Furthermore, learning a new language fosters (21) (CULTURE) awareness and empathy. It provides</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ENRICH</t>
+          <t>awareness and empathy. It provides (22) (ENRICH) experiences by allowing people to connect with others on a deeper level. Despite the</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DIFFICULT</t>
+          <t>experiences by allowing people to connect with others on a deeper level. Despite the (23) (DIFFICULT) of mastering grammar and vocabulary, the long-term rewards are</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DENY</t>
+          <t>of mastering grammar and vocabulary, the long-term rewards are (24) (DENY) worth the effort. By breaking down linguistic barriers, we open ourselves up to new perspectives and opportunities, ultimately becoming more well-rounded citizens of a diverse and interconnected global community, ready to face the challenges of the modern era.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6712,42 +6712,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IMPRESS</t>
+          <t>constantly evolving to meet the needs of a growing population. One of the most (17) (IMPRESS) trends is the shift towards sustainable architecture. This</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MOVE</t>
+          <t>trends is the shift towards sustainable architecture. This (18) (MOVE) focuses on reducing the</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ENVIRONMENT</t>
+          <t>focuses on reducing the (19) (ENVIRONMENT) impact of buildings through smart design. Architects are now</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>INCORPORATE</t>
+          <t>impact of buildings through smart design. Architects are now (20) (INCORPORATE) green roofs and solar panels into their plans. These</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>INNOVATE</t>
+          <t>green roofs and solar panels into their plans. These (21) (INNOVATE) not only save energy but also improve the</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LIVE</t>
+          <t>not only save energy but also improve the (22) (LIVE) of urban areas. Despite the</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>INITIATE</t>
+          <t>of urban areas. Despite the (23) (INITIATE) costs, the long-term benefits for the planet are</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SIGNIFY</t>
+          <t>costs, the long-term benefits for the planet are (24) (SIGNIFY). By prioritizing renewable resources and efficient waste management, the construction industry is helping to build a cleaner future. This holistic approach ensures that our urban centers remain functional and healthy for generations to come, proving that progress and nature can coexist harmoniously when we apply creativity and responsibility to the way we build our homes and workspaces.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
